--- a/master/result/84_重生宫廷_凤鸣九天/84_重生宫廷_凤鸣九天.xlsx
+++ b/master/result/84_重生宫廷_凤鸣九天/84_重生宫廷_凤鸣九天.xlsx
@@ -397,665 +397,843 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:D59"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>happy</v>
       </c>
       <c r="B2" t="str">
-        <v>happy</v>
+        <v>/happy/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>快乐</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>seat</v>
       </c>
       <c r="B3" t="str">
-        <v>seat</v>
+        <v>/seat/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>座位</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>here</v>
       </c>
       <c r="B4" t="str">
-        <v>here</v>
+        <v>/here/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>这里</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>essence</v>
       </c>
       <c r="B5" t="str">
-        <v>essence</v>
+        <v>/essence/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>本质</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>object</v>
       </c>
       <c r="B6" t="str">
-        <v>object</v>
+        <v>/əbˈdʒekt/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>目标</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>assembly</v>
       </c>
       <c r="B7" t="str">
-        <v>assembly</v>
+        <v>/assembly/</v>
       </c>
       <c r="C7" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D7" t="str">
         <v>集合</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>throne</v>
       </c>
       <c r="B8" t="str">
-        <v>throne</v>
+        <v>/throne/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>宝座</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>govern</v>
       </c>
       <c r="B9" t="str">
-        <v>govern</v>
+        <v>/ˈɡʌvən/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>统治</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>garment</v>
       </c>
       <c r="B10" t="str">
-        <v>garment</v>
+        <v>/garment/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>衣服</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>stripe</v>
       </c>
       <c r="B11" t="str">
-        <v>stripe</v>
+        <v>/stripe/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>条纹</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>scarf</v>
       </c>
       <c r="B12" t="str">
-        <v>scarf</v>
+        <v>/scarf/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>围巾</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>pearl</v>
       </c>
       <c r="B13" t="str">
-        <v>pearl</v>
+        <v>/pearl/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>珍珠</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>sector</v>
       </c>
       <c r="B14" t="str">
-        <v>sector</v>
+        <v>/sector/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>区域</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>renovate</v>
       </c>
       <c r="B15" t="str">
-        <v>renovate</v>
+        <v>/renovate/</v>
       </c>
       <c r="C15" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D15" t="str">
         <v>更新</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>leading</v>
       </c>
       <c r="B16" t="str">
-        <v>leading</v>
+        <v>/leading/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>领导</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>usage</v>
       </c>
       <c r="B17" t="str">
-        <v>usage</v>
+        <v>/usage/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>习惯</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>unlike</v>
       </c>
       <c r="B18" t="str">
-        <v>unlike</v>
+        <v>/unlike/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>不同</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>amiable</v>
       </c>
       <c r="B19" t="str">
-        <v>amiable</v>
+        <v>/amiable/</v>
       </c>
       <c r="C19" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>和蔼的</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>couch</v>
       </c>
       <c r="B20" t="str">
-        <v>couch</v>
+        <v>/couch/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>长榻</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>music</v>
       </c>
       <c r="B21" t="str">
-        <v>music</v>
+        <v>/music/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>音乐</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>representative</v>
       </c>
       <c r="B22" t="str">
-        <v>representative</v>
+        <v>/representative/</v>
       </c>
       <c r="C22" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D22" t="str">
         <v>代表</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>splendid</v>
       </c>
       <c r="B23" t="str">
+        <v>/splendid/</v>
+      </c>
+      <c r="C23" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D23" t="str">
+        <v>华丽的</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>nearly</v>
+      </c>
+      <c r="B24" t="str">
+        <v>/nearly/</v>
+      </c>
+      <c r="C24" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D24" t="str">
+        <v>几乎</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>learning</v>
+      </c>
+      <c r="B25" t="str">
+        <v>/learning/</v>
+      </c>
+      <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
+        <v>知识</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>iron</v>
+      </c>
+      <c r="B26" t="str">
+        <v>/iron/</v>
+      </c>
+      <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
+        <v>铁</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>demonstrate</v>
+      </c>
+      <c r="B27" t="str">
+        <v>/demonstrate/</v>
+      </c>
+      <c r="C27" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D27" t="str">
+        <v>演示</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>helpful</v>
+      </c>
+      <c r="B28" t="str">
+        <v>/helpful/</v>
+      </c>
+      <c r="C28" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D28" t="str">
+        <v>有帮助</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>apparatus</v>
+      </c>
+      <c r="B29" t="str">
+        <v>/apparatus/</v>
+      </c>
+      <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
+        <v>仪器</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>supervise</v>
+      </c>
+      <c r="B30" t="str">
+        <v>/supervise/</v>
+      </c>
+      <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
+        <v>监督</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>carpet</v>
+      </c>
+      <c r="B31" t="str">
+        <v>/ˈkɑːpɪt/</v>
+      </c>
+      <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
+        <v>地毯</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>grace</v>
+      </c>
+      <c r="B32" t="str">
+        <v>/grace/</v>
+      </c>
+      <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
+        <v>优雅</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>bulletin</v>
+      </c>
+      <c r="B33" t="str">
+        <v>/bulletin/</v>
+      </c>
+      <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
+        <v>公告</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>false</v>
+      </c>
+      <c r="B34" t="str">
+        <v>/false/</v>
+      </c>
+      <c r="C34" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D34" t="str">
+        <v>虚假的</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>puzzle</v>
+      </c>
+      <c r="B35" t="str">
+        <v>/puzzle/</v>
+      </c>
+      <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
+        <v>谜题</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>hurry</v>
+      </c>
+      <c r="B36" t="str">
+        <v>/ˈhʌri/</v>
+      </c>
+      <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
+        <v>匆忙</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>challenge</v>
+      </c>
+      <c r="B37" t="str">
+        <v>/ˈtʃælɪndʒ/</v>
+      </c>
+      <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
+        <v>挑战</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>clothe</v>
+      </c>
+      <c r="B38" t="str">
+        <v>/clothe/</v>
+      </c>
+      <c r="C38" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D38" t="str">
+        <v>衣服</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>orient</v>
+      </c>
+      <c r="B39" t="str">
+        <v>/orient/</v>
+      </c>
+      <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
+        <v>东方</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>dwell</v>
+      </c>
+      <c r="B40" t="str">
+        <v>/dwell/</v>
+      </c>
+      <c r="C40" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D40" t="str">
+        <v>居住</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>advisable</v>
+      </c>
+      <c r="B41" t="str">
+        <v>/advisable/</v>
+      </c>
+      <c r="C41" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D41" t="str">
+        <v>明智的</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>nut</v>
+      </c>
+      <c r="B42" t="str">
+        <v>/nut/</v>
+      </c>
+      <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
+        <v>坚果</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>alike</v>
+      </c>
+      <c r="B43" t="str">
+        <v>/alike/</v>
+      </c>
+      <c r="C43" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D43" t="str">
+        <v>同样的</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>twinkle</v>
+      </c>
+      <c r="B44" t="str">
+        <v>/twinkle/</v>
+      </c>
+      <c r="C44" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D44" t="str">
+        <v>闪烁</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>move</v>
+      </c>
+      <c r="B45" t="str">
+        <v>/muːv/</v>
+      </c>
+      <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
+        <v>改变</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
         <v>splendid</v>
       </c>
-      <c r="C23" t="str">
-        <v>华丽的</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="str">
-        <v>nearly</v>
-      </c>
-      <c r="C24" t="str">
-        <v>几乎</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="str">
-        <v>learning</v>
-      </c>
-      <c r="C25" t="str">
-        <v>知识</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="str">
-        <v>iron</v>
-      </c>
-      <c r="C26" t="str">
-        <v>铁</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="str">
-        <v>demonstrate</v>
-      </c>
-      <c r="C27" t="str">
-        <v>演示</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="str">
-        <v>helpful</v>
-      </c>
-      <c r="C28" t="str">
-        <v>有帮助</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="str">
-        <v>apparatus</v>
-      </c>
-      <c r="C29" t="str">
-        <v>仪器</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="str">
-        <v>supervise</v>
-      </c>
-      <c r="C30" t="str">
-        <v>监督</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="str">
-        <v>carpet</v>
-      </c>
-      <c r="C31" t="str">
-        <v>地毯</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="str">
-        <v>grace</v>
-      </c>
-      <c r="C32" t="str">
-        <v>优雅</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="str">
-        <v>bulletin</v>
-      </c>
-      <c r="C33" t="str">
-        <v>公告</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="str">
+      <c r="B46" t="str">
+        <v>/splendid/</v>
+      </c>
+      <c r="C46" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D46" t="str">
+        <v>极好</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>pull</v>
+      </c>
+      <c r="B47" t="str">
+        <v>/pʊl/</v>
+      </c>
+      <c r="C47" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D47" t="str">
+        <v>拉</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>blur</v>
+      </c>
+      <c r="B48" t="str">
+        <v>/blur/</v>
+      </c>
+      <c r="C48" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D48" t="str">
+        <v>模糊</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>drop</v>
+      </c>
+      <c r="B49" t="str">
+        <v>/drɒp/</v>
+      </c>
+      <c r="C49" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D49" t="str">
+        <v>落下</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>provoke</v>
+      </c>
+      <c r="B50" t="str">
+        <v>/provoke/</v>
+      </c>
+      <c r="C50" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D50" t="str">
+        <v>激发</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>cosmic</v>
+      </c>
+      <c r="B51" t="str">
+        <v>/cosmic/</v>
+      </c>
+      <c r="C51" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D51" t="str">
+        <v>宇宙</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>saturate</v>
+      </c>
+      <c r="B52" t="str">
+        <v>/saturate/</v>
+      </c>
+      <c r="C52" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D52" t="str">
+        <v>浸透</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>saturate</v>
+      </c>
+      <c r="B53" t="str">
+        <v>/saturate/</v>
+      </c>
+      <c r="C53" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D53" t="str">
+        <v>浸湿</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>accurate</v>
+      </c>
+      <c r="B54" t="str">
+        <v>/ˈækjərət/</v>
+      </c>
+      <c r="C54" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D54" t="str">
+        <v>准确</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>ability</v>
+      </c>
+      <c r="B55" t="str">
+        <v>/əˈbɪləti/</v>
+      </c>
+      <c r="C55" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D55" t="str">
+        <v>能力</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>coincide</v>
+      </c>
+      <c r="B56" t="str">
+        <v>/coincide/</v>
+      </c>
+      <c r="C56" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D56" t="str">
+        <v>巧合</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
         <v>false</v>
       </c>
-      <c r="C34" t="str">
-        <v>虚假的</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="str">
-        <v>puzzle</v>
-      </c>
-      <c r="C35" t="str">
-        <v>谜题</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="str">
-        <v>hurry</v>
-      </c>
-      <c r="C36" t="str">
-        <v>匆忙</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="str">
-        <v>challenge</v>
-      </c>
-      <c r="C37" t="str">
-        <v>挑战</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="str">
-        <v>clothe</v>
-      </c>
-      <c r="C38" t="str">
-        <v>衣服</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>orient</v>
-      </c>
-      <c r="C39" t="str">
-        <v>东方</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>dwell</v>
-      </c>
-      <c r="C40" t="str">
-        <v>居住</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>advisable</v>
-      </c>
-      <c r="C41" t="str">
-        <v>明智的</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>nut</v>
-      </c>
-      <c r="C42" t="str">
-        <v>坚果</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>alike</v>
-      </c>
-      <c r="C43" t="str">
-        <v>同样的</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>twinkle</v>
-      </c>
-      <c r="C44" t="str">
-        <v>闪烁</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>move</v>
-      </c>
-      <c r="C45" t="str">
-        <v>改变</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
+      <c r="B57" t="str">
+        <v>/false/</v>
+      </c>
+      <c r="C57" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D57" t="str">
+        <v>错误</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>represent</v>
+      </c>
+      <c r="B58" t="str">
+        <v>/ˌreprɪˈzent/</v>
+      </c>
+      <c r="C58" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D58" t="str">
+        <v>代表</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
         <v>splendid</v>
       </c>
-      <c r="C46" t="str">
-        <v>极好</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>pull</v>
-      </c>
-      <c r="C47" t="str">
-        <v>拉</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>blur</v>
-      </c>
-      <c r="C48" t="str">
-        <v>模糊</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>drop</v>
-      </c>
-      <c r="C49" t="str">
-        <v>落下</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>provoke</v>
-      </c>
-      <c r="C50" t="str">
-        <v>激发</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>cosmic</v>
-      </c>
-      <c r="C51" t="str">
-        <v>宇宙</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>saturate</v>
-      </c>
-      <c r="C52" t="str">
-        <v>浸透</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>saturate</v>
-      </c>
-      <c r="C53" t="str">
-        <v>浸湿</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>accurate</v>
-      </c>
-      <c r="C54" t="str">
-        <v>准确</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>ability</v>
-      </c>
-      <c r="C55" t="str">
-        <v>能力</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>coincide</v>
-      </c>
-      <c r="C56" t="str">
-        <v>巧合</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>false</v>
-      </c>
-      <c r="C57" t="str">
-        <v>错误</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>represent</v>
-      </c>
-      <c r="C58" t="str">
-        <v>代表</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
       <c r="B59" t="str">
-        <v>splendid</v>
+        <v>/splendid/</v>
       </c>
       <c r="C59" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D59" t="str">
         <v>美好</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D59"/>
   </ignoredErrors>
 </worksheet>
 </file>